--- a/연구코드/data/신촌/landmark/신촌_landmark_body_composition.xlsx
+++ b/연구코드/data/신촌/landmark/신촌_landmark_body_composition.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="38">
   <si>
     <t>PatientID</t>
   </si>
@@ -103,6 +103,9 @@
     <t>PRE  3mm</t>
   </si>
   <si>
+    <t>Pre  2mm</t>
+  </si>
+  <si>
     <t>iCT 256</t>
   </si>
   <si>
@@ -118,7 +121,13 @@
     <t>SOMATOM Definition AS+</t>
   </si>
   <si>
+    <t>SOMATOM Definition Flash</t>
+  </si>
+  <si>
     <t>ok</t>
+  </si>
+  <si>
+    <t>anchor_not_found</t>
   </si>
 </sst>
 </file>
@@ -476,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -540,7 +549,7 @@
         <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H2">
         <v>1.39</v>
@@ -558,7 +567,7 @@
         <v>5.41</v>
       </c>
       <c r="M2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -581,7 +590,7 @@
         <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H3">
         <v>0.22</v>
@@ -599,7 +608,7 @@
         <v>10.03</v>
       </c>
       <c r="M3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -622,7 +631,7 @@
         <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H4">
         <v>0.35</v>
@@ -640,7 +649,7 @@
         <v>8.130000000000001</v>
       </c>
       <c r="M4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -663,7 +672,7 @@
         <v>24</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H5">
         <v>0.57</v>
@@ -681,7 +690,7 @@
         <v>9.31</v>
       </c>
       <c r="M5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -704,7 +713,7 @@
         <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -722,7 +731,7 @@
         <v>5.03</v>
       </c>
       <c r="M6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -745,7 +754,7 @@
         <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H7">
         <v>0.11</v>
@@ -763,7 +772,7 @@
         <v>0.92</v>
       </c>
       <c r="M7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -786,7 +795,7 @@
         <v>24</v>
       </c>
       <c r="G8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -804,7 +813,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -827,7 +836,7 @@
         <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -845,7 +854,7 @@
         <v>0.09</v>
       </c>
       <c r="M9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -868,7 +877,7 @@
         <v>24</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -886,7 +895,7 @@
         <v>1.59</v>
       </c>
       <c r="M10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -909,7 +918,7 @@
         <v>24</v>
       </c>
       <c r="G11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -927,7 +936,7 @@
         <v>4.24</v>
       </c>
       <c r="M11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -950,7 +959,7 @@
         <v>24</v>
       </c>
       <c r="G12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -968,7 +977,7 @@
         <v>5.42</v>
       </c>
       <c r="M12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -991,7 +1000,7 @@
         <v>25</v>
       </c>
       <c r="G13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H13">
         <v>2.18</v>
@@ -1009,7 +1018,7 @@
         <v>2.48</v>
       </c>
       <c r="M13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1032,7 +1041,7 @@
         <v>25</v>
       </c>
       <c r="G14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H14">
         <v>0.11</v>
@@ -1050,7 +1059,7 @@
         <v>4.62</v>
       </c>
       <c r="M14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1073,7 +1082,7 @@
         <v>25</v>
       </c>
       <c r="G15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H15">
         <v>1.19</v>
@@ -1091,7 +1100,7 @@
         <v>5.95</v>
       </c>
       <c r="M15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1114,7 +1123,7 @@
         <v>25</v>
       </c>
       <c r="G16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H16">
         <v>0.16</v>
@@ -1132,7 +1141,7 @@
         <v>3.37</v>
       </c>
       <c r="M16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1155,7 +1164,7 @@
         <v>25</v>
       </c>
       <c r="G17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H17">
         <v>0.21</v>
@@ -1173,7 +1182,7 @@
         <v>0.36</v>
       </c>
       <c r="M17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1196,7 +1205,7 @@
         <v>25</v>
       </c>
       <c r="G18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H18">
         <v>1.92</v>
@@ -1214,7 +1223,7 @@
         <v>1.84</v>
       </c>
       <c r="M18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1237,7 +1246,7 @@
         <v>25</v>
       </c>
       <c r="G19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H19">
         <v>0.13</v>
@@ -1255,7 +1264,7 @@
         <v>1.65</v>
       </c>
       <c r="M19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1278,7 +1287,7 @@
         <v>25</v>
       </c>
       <c r="G20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H20">
         <v>0.16</v>
@@ -1296,7 +1305,7 @@
         <v>0.44</v>
       </c>
       <c r="M20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1319,7 +1328,7 @@
         <v>25</v>
       </c>
       <c r="G21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H21">
         <v>0.6</v>
@@ -1337,7 +1346,7 @@
         <v>2</v>
       </c>
       <c r="M21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1360,7 +1369,7 @@
         <v>25</v>
       </c>
       <c r="G22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H22">
         <v>0.83</v>
@@ -1378,7 +1387,7 @@
         <v>4.23</v>
       </c>
       <c r="M22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1401,7 +1410,7 @@
         <v>25</v>
       </c>
       <c r="G23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -1419,7 +1428,7 @@
         <v>7.04</v>
       </c>
       <c r="M23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1442,7 +1451,7 @@
         <v>26</v>
       </c>
       <c r="G24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H24">
         <v>0.13</v>
@@ -1460,7 +1469,7 @@
         <v>5.63</v>
       </c>
       <c r="M24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1483,7 +1492,7 @@
         <v>26</v>
       </c>
       <c r="G25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H25">
         <v>0.85</v>
@@ -1501,7 +1510,7 @@
         <v>5.45</v>
       </c>
       <c r="M25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1524,7 +1533,7 @@
         <v>26</v>
       </c>
       <c r="G26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H26">
         <v>1.14</v>
@@ -1542,7 +1551,7 @@
         <v>2.34</v>
       </c>
       <c r="M26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1565,7 +1574,7 @@
         <v>26</v>
       </c>
       <c r="G27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H27">
         <v>0.17</v>
@@ -1583,7 +1592,7 @@
         <v>2.48</v>
       </c>
       <c r="M27" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1606,7 +1615,7 @@
         <v>26</v>
       </c>
       <c r="G28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H28">
         <v>0.82</v>
@@ -1624,7 +1633,7 @@
         <v>2.75</v>
       </c>
       <c r="M28" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1647,7 +1656,7 @@
         <v>26</v>
       </c>
       <c r="G29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H29">
         <v>0.24</v>
@@ -1665,7 +1674,7 @@
         <v>2</v>
       </c>
       <c r="M29" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1688,7 +1697,7 @@
         <v>26</v>
       </c>
       <c r="G30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -1706,7 +1715,7 @@
         <v>0.87</v>
       </c>
       <c r="M30" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1729,7 +1738,7 @@
         <v>26</v>
       </c>
       <c r="G31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H31">
         <v>0.04</v>
@@ -1747,7 +1756,7 @@
         <v>0.32</v>
       </c>
       <c r="M31" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1770,7 +1779,7 @@
         <v>26</v>
       </c>
       <c r="G32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H32">
         <v>1.38</v>
@@ -1788,7 +1797,7 @@
         <v>5.46</v>
       </c>
       <c r="M32" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1811,7 +1820,7 @@
         <v>26</v>
       </c>
       <c r="G33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H33">
         <v>0.49</v>
@@ -1829,7 +1838,7 @@
         <v>3.22</v>
       </c>
       <c r="M33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -1852,7 +1861,7 @@
         <v>26</v>
       </c>
       <c r="G34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H34">
         <v>0.28</v>
@@ -1870,7 +1879,7 @@
         <v>3.07</v>
       </c>
       <c r="M34" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -1893,7 +1902,7 @@
         <v>27</v>
       </c>
       <c r="G35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H35">
         <v>1.83</v>
@@ -1911,7 +1920,7 @@
         <v>9.51</v>
       </c>
       <c r="M35" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -1934,7 +1943,7 @@
         <v>27</v>
       </c>
       <c r="G36" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H36">
         <v>1.83</v>
@@ -1952,7 +1961,7 @@
         <v>9.51</v>
       </c>
       <c r="M36" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -1975,7 +1984,7 @@
         <v>27</v>
       </c>
       <c r="G37" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H37">
         <v>1.4</v>
@@ -1993,7 +2002,7 @@
         <v>3</v>
       </c>
       <c r="M37" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -2016,7 +2025,7 @@
         <v>27</v>
       </c>
       <c r="G38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H38">
         <v>1.04</v>
@@ -2034,7 +2043,7 @@
         <v>5.55</v>
       </c>
       <c r="M38" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -2057,7 +2066,7 @@
         <v>27</v>
       </c>
       <c r="G39" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H39">
         <v>0.13</v>
@@ -2075,7 +2084,7 @@
         <v>3.89</v>
       </c>
       <c r="M39" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -2098,7 +2107,7 @@
         <v>27</v>
       </c>
       <c r="G40" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H40">
         <v>0.21</v>
@@ -2116,7 +2125,7 @@
         <v>2.76</v>
       </c>
       <c r="M40" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -2139,7 +2148,7 @@
         <v>27</v>
       </c>
       <c r="G41" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H41">
         <v>1.67</v>
@@ -2157,7 +2166,7 @@
         <v>3.78</v>
       </c>
       <c r="M41" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -2180,7 +2189,7 @@
         <v>27</v>
       </c>
       <c r="G42" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H42">
         <v>0.17</v>
@@ -2198,7 +2207,7 @@
         <v>0.67</v>
       </c>
       <c r="M42" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -2221,7 +2230,7 @@
         <v>27</v>
       </c>
       <c r="G43" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H43">
         <v>3.43</v>
@@ -2239,7 +2248,7 @@
         <v>2.88</v>
       </c>
       <c r="M43" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -2262,7 +2271,7 @@
         <v>27</v>
       </c>
       <c r="G44" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H44">
         <v>1.83</v>
@@ -2280,7 +2289,7 @@
         <v>3.75</v>
       </c>
       <c r="M44" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -2303,7 +2312,7 @@
         <v>27</v>
       </c>
       <c r="G45" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H45">
         <v>0.04</v>
@@ -2321,7 +2330,7 @@
         <v>8.390000000000001</v>
       </c>
       <c r="M45" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -2344,7 +2353,7 @@
         <v>25</v>
       </c>
       <c r="G46" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H46">
         <v>1.87</v>
@@ -2362,7 +2371,7 @@
         <v>2.72</v>
       </c>
       <c r="M46" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -2385,7 +2394,7 @@
         <v>25</v>
       </c>
       <c r="G47" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H47">
         <v>1.46</v>
@@ -2403,7 +2412,7 @@
         <v>0.85</v>
       </c>
       <c r="M47" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -2426,7 +2435,7 @@
         <v>25</v>
       </c>
       <c r="G48" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H48">
         <v>3.09</v>
@@ -2444,7 +2453,7 @@
         <v>0.11</v>
       </c>
       <c r="M48" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2467,7 +2476,7 @@
         <v>25</v>
       </c>
       <c r="G49" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H49">
         <v>2.01</v>
@@ -2485,7 +2494,7 @@
         <v>1.67</v>
       </c>
       <c r="M49" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2508,7 +2517,7 @@
         <v>25</v>
       </c>
       <c r="G50" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H50">
         <v>1.02</v>
@@ -2526,7 +2535,7 @@
         <v>2</v>
       </c>
       <c r="M50" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -2549,7 +2558,7 @@
         <v>25</v>
       </c>
       <c r="G51" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H51">
         <v>0.76</v>
@@ -2567,7 +2576,7 @@
         <v>2.35</v>
       </c>
       <c r="M51" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2590,7 +2599,7 @@
         <v>25</v>
       </c>
       <c r="G52" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H52">
         <v>0.19</v>
@@ -2608,7 +2617,7 @@
         <v>1.93</v>
       </c>
       <c r="M52" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2631,7 +2640,7 @@
         <v>25</v>
       </c>
       <c r="G53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H53">
         <v>0.85</v>
@@ -2649,7 +2658,7 @@
         <v>0.47</v>
       </c>
       <c r="M53" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -2672,7 +2681,7 @@
         <v>25</v>
       </c>
       <c r="G54" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H54">
         <v>0.42</v>
@@ -2690,7 +2699,7 @@
         <v>4.65</v>
       </c>
       <c r="M54" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -2713,7 +2722,7 @@
         <v>25</v>
       </c>
       <c r="G55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H55">
         <v>1.28</v>
@@ -2731,7 +2740,7 @@
         <v>3.78</v>
       </c>
       <c r="M55" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -2754,7 +2763,7 @@
         <v>25</v>
       </c>
       <c r="G56" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H56">
         <v>0.48</v>
@@ -2772,7 +2781,7 @@
         <v>1.4</v>
       </c>
       <c r="M56" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -2795,7 +2804,7 @@
         <v>28</v>
       </c>
       <c r="G57" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H57">
         <v>2.43</v>
@@ -2813,7 +2822,7 @@
         <v>5.68</v>
       </c>
       <c r="M57" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -2836,7 +2845,7 @@
         <v>28</v>
       </c>
       <c r="G58" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H58">
         <v>1.71</v>
@@ -2854,7 +2863,7 @@
         <v>7.71</v>
       </c>
       <c r="M58" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -2877,7 +2886,7 @@
         <v>28</v>
       </c>
       <c r="G59" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H59">
         <v>2.23</v>
@@ -2895,7 +2904,7 @@
         <v>5.65</v>
       </c>
       <c r="M59" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -2918,7 +2927,7 @@
         <v>28</v>
       </c>
       <c r="G60" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H60">
         <v>0.25</v>
@@ -2936,7 +2945,7 @@
         <v>4.22</v>
       </c>
       <c r="M60" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -2959,7 +2968,7 @@
         <v>28</v>
       </c>
       <c r="G61" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H61">
         <v>0.25</v>
@@ -2977,7 +2986,7 @@
         <v>4.4</v>
       </c>
       <c r="M61" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -3000,7 +3009,7 @@
         <v>28</v>
       </c>
       <c r="G62" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H62">
         <v>0.06</v>
@@ -3018,7 +3027,7 @@
         <v>2.06</v>
       </c>
       <c r="M62" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -3041,7 +3050,7 @@
         <v>28</v>
       </c>
       <c r="G63" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -3059,7 +3068,7 @@
         <v>5.2</v>
       </c>
       <c r="M63" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -3082,7 +3091,7 @@
         <v>28</v>
       </c>
       <c r="G64" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -3100,7 +3109,7 @@
         <v>3.21</v>
       </c>
       <c r="M64" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -3123,7 +3132,7 @@
         <v>28</v>
       </c>
       <c r="G65" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -3141,7 +3150,7 @@
         <v>6.28</v>
       </c>
       <c r="M65" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -3164,7 +3173,7 @@
         <v>28</v>
       </c>
       <c r="G66" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H66">
         <v>0.6</v>
@@ -3182,7 +3191,7 @@
         <v>5.33</v>
       </c>
       <c r="M66" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -3205,7 +3214,7 @@
         <v>28</v>
       </c>
       <c r="G67" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H67">
         <v>1.04</v>
@@ -3223,7 +3232,410 @@
         <v>2.04</v>
       </c>
       <c r="M67" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13">
+      <c r="A68">
+        <v>294928</v>
+      </c>
+      <c r="B68" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68">
+        <v>128</v>
+      </c>
+      <c r="D68">
+        <v>19</v>
+      </c>
+      <c r="E68">
+        <v>-21.9</v>
+      </c>
+      <c r="F68" t="s">
+        <v>29</v>
+      </c>
+      <c r="G68" t="s">
+        <v>35</v>
+      </c>
+      <c r="H68">
+        <v>1.35</v>
+      </c>
+      <c r="I68">
+        <v>9.57</v>
+      </c>
+      <c r="J68">
+        <v>2.03</v>
+      </c>
+      <c r="K68">
+        <v>7.06</v>
+      </c>
+      <c r="L68">
+        <v>7.52</v>
+      </c>
+      <c r="M68" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13">
+      <c r="A69">
+        <v>294928</v>
+      </c>
+      <c r="B69" t="s">
+        <v>14</v>
+      </c>
+      <c r="C69">
+        <v>106</v>
+      </c>
+      <c r="D69">
+        <v>41</v>
+      </c>
+      <c r="E69">
+        <v>-65.90000000000001</v>
+      </c>
+      <c r="F69" t="s">
+        <v>29</v>
+      </c>
+      <c r="G69" t="s">
+        <v>35</v>
+      </c>
+      <c r="H69">
+        <v>0.6</v>
+      </c>
+      <c r="I69">
+        <v>10.46</v>
+      </c>
+      <c r="J69">
+        <v>1.52</v>
+      </c>
+      <c r="K69">
+        <v>5.04</v>
+      </c>
+      <c r="L69">
+        <v>2.68</v>
+      </c>
+      <c r="M69" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13">
+      <c r="A70">
+        <v>294928</v>
+      </c>
+      <c r="B70" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70">
+        <v>92</v>
+      </c>
+      <c r="D70">
+        <v>55</v>
+      </c>
+      <c r="E70">
+        <v>-93.90000000000001</v>
+      </c>
+      <c r="F70" t="s">
+        <v>29</v>
+      </c>
+      <c r="G70" t="s">
+        <v>35</v>
+      </c>
+      <c r="H70">
+        <v>0.06</v>
+      </c>
+      <c r="I70">
+        <v>5.9</v>
+      </c>
+      <c r="J70">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="K70">
+        <v>2.73</v>
+      </c>
+      <c r="L70">
+        <v>0.85</v>
+      </c>
+      <c r="M70" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13">
+      <c r="A71">
+        <v>294928</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71">
+        <v>77</v>
+      </c>
+      <c r="D71">
+        <v>70</v>
+      </c>
+      <c r="E71">
+        <v>-123.9</v>
+      </c>
+      <c r="F71" t="s">
+        <v>29</v>
+      </c>
+      <c r="G71" t="s">
+        <v>35</v>
+      </c>
+      <c r="H71">
+        <v>0.17</v>
+      </c>
+      <c r="I71">
+        <v>5.56</v>
+      </c>
+      <c r="J71">
+        <v>1.06</v>
+      </c>
+      <c r="K71">
+        <v>2.62</v>
+      </c>
+      <c r="L71">
+        <v>0.62</v>
+      </c>
+      <c r="M71" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13">
+      <c r="A72">
+        <v>294928</v>
+      </c>
+      <c r="B72" t="s">
+        <v>17</v>
+      </c>
+      <c r="C72">
+        <v>61</v>
+      </c>
+      <c r="D72">
+        <v>86</v>
+      </c>
+      <c r="E72">
+        <v>-155.9</v>
+      </c>
+      <c r="F72" t="s">
+        <v>29</v>
+      </c>
+      <c r="G72" t="s">
+        <v>35</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>3.05</v>
+      </c>
+      <c r="J72">
+        <v>0.18</v>
+      </c>
+      <c r="K72">
+        <v>0.9</v>
+      </c>
+      <c r="L72">
+        <v>1.03</v>
+      </c>
+      <c r="M72" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13">
+      <c r="A73">
+        <v>294928</v>
+      </c>
+      <c r="B73" t="s">
+        <v>18</v>
+      </c>
+      <c r="C73">
+        <v>44</v>
+      </c>
+      <c r="D73">
+        <v>103</v>
+      </c>
+      <c r="E73">
+        <v>-189.9</v>
+      </c>
+      <c r="F73" t="s">
+        <v>29</v>
+      </c>
+      <c r="G73" t="s">
+        <v>35</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>2.85</v>
+      </c>
+      <c r="J73">
+        <v>0.66</v>
+      </c>
+      <c r="K73">
+        <v>2.69</v>
+      </c>
+      <c r="L73">
+        <v>1.42</v>
+      </c>
+      <c r="M73" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13">
+      <c r="A74">
+        <v>294928</v>
+      </c>
+      <c r="B74" t="s">
+        <v>19</v>
+      </c>
+      <c r="C74">
+        <v>26</v>
+      </c>
+      <c r="D74">
+        <v>121</v>
+      </c>
+      <c r="E74">
+        <v>-225.9</v>
+      </c>
+      <c r="F74" t="s">
+        <v>29</v>
+      </c>
+      <c r="G74" t="s">
+        <v>35</v>
+      </c>
+      <c r="H74">
+        <v>0.12</v>
+      </c>
+      <c r="I74">
+        <v>0.42</v>
+      </c>
+      <c r="J74">
+        <v>0.36</v>
+      </c>
+      <c r="K74">
+        <v>1.75</v>
+      </c>
+      <c r="L74">
+        <v>2.24</v>
+      </c>
+      <c r="M74" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13">
+      <c r="A75">
+        <v>294928</v>
+      </c>
+      <c r="B75" t="s">
+        <v>20</v>
+      </c>
+      <c r="C75">
+        <v>8</v>
+      </c>
+      <c r="D75">
+        <v>139</v>
+      </c>
+      <c r="E75">
+        <v>-261.9</v>
+      </c>
+      <c r="F75" t="s">
+        <v>29</v>
+      </c>
+      <c r="G75" t="s">
+        <v>35</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>0.51</v>
+      </c>
+      <c r="J75">
+        <v>0.09</v>
+      </c>
+      <c r="K75">
+        <v>0.5</v>
+      </c>
+      <c r="L75">
+        <v>0.67</v>
+      </c>
+      <c r="M75" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13">
+      <c r="A76">
+        <v>294928</v>
+      </c>
+      <c r="B76" t="s">
+        <v>21</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+      <c r="D76">
+        <v>146</v>
+      </c>
+      <c r="E76">
+        <v>-275.9</v>
+      </c>
+      <c r="F76" t="s">
+        <v>29</v>
+      </c>
+      <c r="G76" t="s">
+        <v>35</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>1.28</v>
+      </c>
+      <c r="J76">
+        <v>0.32</v>
+      </c>
+      <c r="K76">
+        <v>1.23</v>
+      </c>
+      <c r="L76">
+        <v>1.02</v>
+      </c>
+      <c r="M76" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13">
+      <c r="A77">
+        <v>294928</v>
+      </c>
+      <c r="B77" t="s">
+        <v>22</v>
+      </c>
+      <c r="F77" t="s">
+        <v>29</v>
+      </c>
+      <c r="G77" t="s">
+        <v>35</v>
+      </c>
+      <c r="M77" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13">
+      <c r="A78">
+        <v>294928</v>
+      </c>
+      <c r="B78" t="s">
+        <v>23</v>
+      </c>
+      <c r="F78" t="s">
+        <v>29</v>
+      </c>
+      <c r="G78" t="s">
+        <v>35</v>
+      </c>
+      <c r="M78" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
